--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484612_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484612_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>7.6945</v>
+        <v>8.0746</v>
       </c>
       <c r="E2" t="n">
-        <v>5.6943</v>
+        <v>5.6532</v>
       </c>
       <c r="F2" t="n">
-        <v>2.0002</v>
+        <v>2.4213</v>
       </c>
       <c r="G2" t="n">
         <v>4.9771</v>
@@ -610,13 +610,13 @@
         <v>2.1991</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.6725</v>
+        <v>-0.2924</v>
       </c>
       <c r="T2" t="n">
-        <v>0.089</v>
+        <v>0.0479</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.7615</v>
+        <v>-0.3403</v>
       </c>
       <c r="V2" t="n">
         <v>4.1229</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>M. LARA BARRACHINA</t>
+          <t>L. GARCIA JIMENEZ</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.2469</v>
+        <v>2.606</v>
       </c>
       <c r="E3" t="n">
-        <v>-1.3999</v>
+        <v>2.8062</v>
       </c>
       <c r="F3" t="n">
-        <v>3.6468</v>
+        <v>-0.2002</v>
       </c>
       <c r="G3" t="n">
-        <v>-0.2248</v>
+        <v>4.2025</v>
       </c>
       <c r="H3" t="n">
-        <v>-1.6284</v>
+        <v>1.7662</v>
       </c>
       <c r="I3" t="n">
-        <v>1.4036</v>
+        <v>2.4362</v>
       </c>
       <c r="J3" t="n">
-        <v>-1.2927</v>
+        <v>3.7267</v>
       </c>
       <c r="K3" t="n">
-        <v>-1.5428</v>
+        <v>1.6748</v>
       </c>
       <c r="L3" t="n">
-        <v>0.25</v>
+        <v>2.0519</v>
       </c>
       <c r="M3" t="n">
-        <v>1.0679</v>
+        <v>0.4757</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.0857</v>
+        <v>0.0914</v>
       </c>
       <c r="O3" t="n">
-        <v>1.1535</v>
+        <v>0.3843</v>
       </c>
       <c r="P3" t="n">
-        <v>-0.733</v>
+        <v>0.1833</v>
       </c>
       <c r="Q3" t="n">
-        <v>-2.1991</v>
+        <v>-1.8326</v>
       </c>
       <c r="R3" t="n">
-        <v>1.4661</v>
+        <v>2.0158</v>
       </c>
       <c r="S3" t="n">
-        <v>0.6708</v>
+        <v>-0.2012</v>
       </c>
       <c r="T3" t="n">
-        <v>0.181</v>
+        <v>0.2681</v>
       </c>
       <c r="U3" t="n">
-        <v>0.4898</v>
+        <v>-0.4693</v>
       </c>
       <c r="V3" t="n">
-        <v>2.5339</v>
+        <v>-1.5785</v>
       </c>
       <c r="W3" t="n">
-        <v>1.9109</v>
+        <v>0.6439</v>
       </c>
       <c r="X3" t="n">
-        <v>0.6231</v>
+        <v>-2.2224</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>L. GARCIA JIMENEZ</t>
+          <t>M. LARA BARRACHINA</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,67 +721,67 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.226</v>
+        <v>1.8342</v>
       </c>
       <c r="E4" t="n">
-        <v>2.8473</v>
+        <v>-1.441</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.6213</v>
+        <v>3.2752</v>
       </c>
       <c r="G4" t="n">
-        <v>4.2025</v>
+        <v>-0.2248</v>
       </c>
       <c r="H4" t="n">
-        <v>1.7662</v>
+        <v>-1.6284</v>
       </c>
       <c r="I4" t="n">
-        <v>2.4362</v>
+        <v>1.4036</v>
       </c>
       <c r="J4" t="n">
-        <v>3.7267</v>
+        <v>-1.2927</v>
       </c>
       <c r="K4" t="n">
-        <v>1.6748</v>
+        <v>-1.5428</v>
       </c>
       <c r="L4" t="n">
-        <v>2.0519</v>
+        <v>0.25</v>
       </c>
       <c r="M4" t="n">
-        <v>0.4757</v>
+        <v>1.0679</v>
       </c>
       <c r="N4" t="n">
-        <v>0.0914</v>
+        <v>-0.0857</v>
       </c>
       <c r="O4" t="n">
-        <v>0.3843</v>
+        <v>1.1535</v>
       </c>
       <c r="P4" t="n">
-        <v>0.1833</v>
+        <v>-0.733</v>
       </c>
       <c r="Q4" t="n">
-        <v>-1.8326</v>
+        <v>-2.1991</v>
       </c>
       <c r="R4" t="n">
-        <v>2.0158</v>
+        <v>1.4661</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.5812</v>
+        <v>0.2581</v>
       </c>
       <c r="T4" t="n">
-        <v>0.3092</v>
+        <v>0.1399</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.8904</v>
+        <v>0.1182</v>
       </c>
       <c r="V4" t="n">
-        <v>-1.5785</v>
+        <v>2.5339</v>
       </c>
       <c r="W4" t="n">
-        <v>0.6439</v>
+        <v>1.9109</v>
       </c>
       <c r="X4" t="n">
-        <v>-2.2224</v>
+        <v>0.6231</v>
       </c>
     </row>
     <row r="5">
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.4386</v>
+        <v>0.9302</v>
       </c>
       <c r="E5" t="n">
-        <v>0.5758</v>
+        <v>0.1912</v>
       </c>
       <c r="F5" t="n">
-        <v>0.8628</v>
+        <v>0.7389</v>
       </c>
       <c r="G5" t="n">
         <v>0.1178</v>
@@ -844,13 +844,13 @@
         <v>1.2828</v>
       </c>
       <c r="S5" t="n">
-        <v>0.3209</v>
+        <v>-0.1876</v>
       </c>
       <c r="T5" t="n">
-        <v>0.3839</v>
+        <v>-0.0007</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.063</v>
+        <v>-0.1869</v>
       </c>
       <c r="V5" t="n">
         <v>0.6335</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>J. TALLON GUIA</t>
+          <t>J. MARIA VENTURA</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.2879</v>
+        <v>0.0868</v>
       </c>
       <c r="E6" t="n">
-        <v>-1.6838</v>
+        <v>1.7565</v>
       </c>
       <c r="F6" t="n">
-        <v>1.9718</v>
+        <v>-1.6697</v>
       </c>
       <c r="G6" t="n">
-        <v>1.3898</v>
+        <v>2.5789</v>
       </c>
       <c r="H6" t="n">
-        <v>0.1462</v>
+        <v>-0.3288</v>
       </c>
       <c r="I6" t="n">
-        <v>1.2436</v>
+        <v>2.9077</v>
       </c>
       <c r="J6" t="n">
-        <v>0.2392</v>
+        <v>2.4861</v>
       </c>
       <c r="K6" t="n">
-        <v>0.2135</v>
+        <v>-0.1333</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0258</v>
+        <v>2.6194</v>
       </c>
       <c r="M6" t="n">
-        <v>1.1505</v>
+        <v>0.09279999999999999</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.0673</v>
+        <v>-0.1955</v>
       </c>
       <c r="O6" t="n">
-        <v>1.2178</v>
+        <v>0.2882</v>
       </c>
       <c r="P6" t="n">
-        <v>-2.0158</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>-3.1154</v>
+        <v>-0.9163</v>
       </c>
       <c r="R6" t="n">
-        <v>1.0995</v>
+        <v>0.9163</v>
       </c>
       <c r="S6" t="n">
-        <v>0.2909</v>
+        <v>0.0418</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.0746</v>
+        <v>0.1867</v>
       </c>
       <c r="U6" t="n">
-        <v>0.3656</v>
+        <v>-0.1448</v>
       </c>
       <c r="V6" t="n">
-        <v>0.6231</v>
+        <v>-2.5339</v>
       </c>
       <c r="W6" t="n">
-        <v>1.267</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.6439</v>
+        <v>-2.5339</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>J. MARIA VENTURA</t>
+          <t>J. TALLON GUIA</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.1635</v>
+        <v>-0.1026</v>
       </c>
       <c r="E7" t="n">
-        <v>1.6053</v>
+        <v>-1.8761</v>
       </c>
       <c r="F7" t="n">
-        <v>-1.7688</v>
+        <v>1.7736</v>
       </c>
       <c r="G7" t="n">
-        <v>2.5789</v>
+        <v>1.3898</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.3288</v>
+        <v>0.1462</v>
       </c>
       <c r="I7" t="n">
-        <v>2.9077</v>
+        <v>1.2436</v>
       </c>
       <c r="J7" t="n">
-        <v>2.4861</v>
+        <v>0.2392</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.1333</v>
+        <v>0.2135</v>
       </c>
       <c r="L7" t="n">
-        <v>2.6194</v>
+        <v>0.0258</v>
       </c>
       <c r="M7" t="n">
-        <v>0.09279999999999999</v>
+        <v>1.1505</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.1955</v>
+        <v>-0.0673</v>
       </c>
       <c r="O7" t="n">
-        <v>0.2882</v>
+        <v>1.2178</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>-2.0158</v>
       </c>
       <c r="Q7" t="n">
-        <v>-0.9163</v>
+        <v>-3.1154</v>
       </c>
       <c r="R7" t="n">
-        <v>0.9163</v>
+        <v>1.0995</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.2085</v>
+        <v>-0.09959999999999999</v>
       </c>
       <c r="T7" t="n">
-        <v>0.0355</v>
+        <v>-0.267</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.2439</v>
+        <v>0.1674</v>
       </c>
       <c r="V7" t="n">
-        <v>-2.5339</v>
+        <v>0.6231</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>1.267</v>
       </c>
       <c r="X7" t="n">
-        <v>-2.5339</v>
+        <v>-0.6439</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>J. TORRES HERNANDO</t>
+          <t>D. SAEZ GIL</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.8507</v>
+        <v>-0.7923</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.9713000000000001</v>
+        <v>-1.9005</v>
       </c>
       <c r="F8" t="n">
-        <v>0.1207</v>
+        <v>1.1083</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.0885</v>
+        <v>2.1492</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.0885</v>
+        <v>1.0275</v>
       </c>
       <c r="I8" t="n">
-        <v>0</v>
+        <v>1.1217</v>
       </c>
       <c r="J8" t="n">
-        <v>0</v>
+        <v>1.4246</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>1.2322</v>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>0.1925</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.0885</v>
+        <v>0.7246</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.0885</v>
+        <v>-0.2047</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>0.9293</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.9163</v>
+        <v>-2.3823</v>
       </c>
       <c r="Q8" t="n">
-        <v>-0.9163</v>
+        <v>-3.6651</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>1.2828</v>
       </c>
       <c r="S8" t="n">
-        <v>0.1541</v>
+        <v>-0.2372</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.0551</v>
+        <v>-0.3039</v>
       </c>
       <c r="U8" t="n">
-        <v>0.2092</v>
+        <v>0.0667</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>-0.3219</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>0.6439</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>-0.9658</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>D. SAEZ GIL</t>
+          <t>J. TORRES HERNANDO</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.2756</v>
+        <v>-0.9498</v>
       </c>
       <c r="E9" t="n">
-        <v>-2.5325</v>
+        <v>-0.9713000000000001</v>
       </c>
       <c r="F9" t="n">
-        <v>1.2569</v>
+        <v>0.0216</v>
       </c>
       <c r="G9" t="n">
-        <v>2.1492</v>
+        <v>-0.0885</v>
       </c>
       <c r="H9" t="n">
-        <v>1.0275</v>
+        <v>-0.0885</v>
       </c>
       <c r="I9" t="n">
-        <v>1.1217</v>
+        <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>1.4246</v>
+        <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>1.2322</v>
+        <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>0.1925</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>0.7246</v>
+        <v>-0.0885</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.2047</v>
+        <v>-0.0885</v>
       </c>
       <c r="O9" t="n">
-        <v>0.9293</v>
+        <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>-2.3823</v>
+        <v>-0.9163</v>
       </c>
       <c r="Q9" t="n">
-        <v>-3.6651</v>
+        <v>-0.9163</v>
       </c>
       <c r="R9" t="n">
-        <v>1.2828</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.7205</v>
+        <v>0.0551</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.9359</v>
+        <v>-0.0551</v>
       </c>
       <c r="U9" t="n">
-        <v>0.2154</v>
+        <v>0.1101</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.3219</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>0.6439</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-0.9658</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>B. KABASELE KATUMBA</t>
+          <t>F. TORCOLETTI</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,64 +1189,64 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.1252</v>
+        <v>-2.0979</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.2027</v>
+        <v>-1.6672</v>
       </c>
       <c r="F10" t="n">
-        <v>0.0775</v>
+        <v>-0.4307</v>
       </c>
       <c r="G10" t="n">
-        <v>0.2568</v>
+        <v>-0.1351</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.2656</v>
+        <v>-0.3145</v>
       </c>
       <c r="I10" t="n">
-        <v>0.5224</v>
+        <v>0.1794</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.5994</v>
+        <v>-0.5577</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.641</v>
+        <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>0.0417</v>
+        <v>-0.5577</v>
       </c>
       <c r="M10" t="n">
-        <v>0.8561</v>
+        <v>0.4226</v>
       </c>
       <c r="N10" t="n">
-        <v>0.3754</v>
+        <v>-0.3145</v>
       </c>
       <c r="O10" t="n">
-        <v>0.4807</v>
+        <v>0.7371</v>
       </c>
       <c r="P10" t="n">
-        <v>-1.6493</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>-2.1991</v>
+        <v>-0.3665</v>
       </c>
       <c r="R10" t="n">
-        <v>0.5498</v>
+        <v>0.3665</v>
       </c>
       <c r="S10" t="n">
-        <v>0.2124</v>
+        <v>-0.0728</v>
       </c>
       <c r="T10" t="n">
-        <v>0.2738</v>
+        <v>-0.1199</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.0614</v>
+        <v>0.0471</v>
       </c>
       <c r="V10" t="n">
-        <v>-0.945</v>
+        <v>-1.89</v>
       </c>
       <c r="W10" t="n">
-        <v>0.3219</v>
+        <v>-0.6231</v>
       </c>
       <c r="X10" t="n">
         <v>-1.267</v>
@@ -1255,7 +1255,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>F. TORCOLETTI</t>
+          <t>B. KABASELE KATUMBA</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,64 +1267,64 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.1415</v>
+        <v>-2.1223</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.8595</v>
+        <v>-2.2989</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.2821</v>
+        <v>0.1766</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.1351</v>
+        <v>0.2568</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.3145</v>
+        <v>-0.2656</v>
       </c>
       <c r="I11" t="n">
-        <v>0.1794</v>
+        <v>0.5224</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.5577</v>
+        <v>-0.5994</v>
       </c>
       <c r="K11" t="n">
-        <v>0</v>
+        <v>-0.641</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.5577</v>
+        <v>0.0417</v>
       </c>
       <c r="M11" t="n">
-        <v>0.4226</v>
+        <v>0.8561</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.3145</v>
+        <v>0.3754</v>
       </c>
       <c r="O11" t="n">
-        <v>0.7371</v>
+        <v>0.4807</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>-1.6493</v>
       </c>
       <c r="Q11" t="n">
-        <v>-0.3665</v>
+        <v>-2.1991</v>
       </c>
       <c r="R11" t="n">
-        <v>0.3665</v>
+        <v>0.5498</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.1164</v>
+        <v>0.2153</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.3122</v>
+        <v>0.1776</v>
       </c>
       <c r="U11" t="n">
-        <v>0.1958</v>
+        <v>0.0377</v>
       </c>
       <c r="V11" t="n">
-        <v>-1.89</v>
+        <v>-0.945</v>
       </c>
       <c r="W11" t="n">
-        <v>-0.6231</v>
+        <v>0.3219</v>
       </c>
       <c r="X11" t="n">
         <v>-1.267</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-2.7046</v>
+        <v>-2.5589</v>
       </c>
       <c r="E12" t="n">
-        <v>-3.4664</v>
+        <v>-3.3703</v>
       </c>
       <c r="F12" t="n">
-        <v>0.7618</v>
+        <v>0.8114</v>
       </c>
       <c r="G12" t="n">
         <v>-1.6013</v>
@@ -1390,13 +1390,13 @@
         <v>0.733</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.4436</v>
+        <v>-0.2979</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.2753</v>
+        <v>-0.1791</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.1683</v>
+        <v>-0.1188</v>
       </c>
       <c r="V12" t="n">
         <v>0.6231</v>
@@ -1423,10 +1423,10 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>4.632799999999999</v>
+        <v>4.908000000000001</v>
       </c>
       <c r="E13" t="n">
-        <v>-3.393399999999999</v>
+        <v>-3.118200000000001</v>
       </c>
       <c r="F13" t="n">
         <v>8.026300000000001</v>
@@ -1444,7 +1444,7 @@
         <v>9.130400000000002</v>
       </c>
       <c r="K13" t="n">
-        <v>5.602600000000002</v>
+        <v>5.602600000000001</v>
       </c>
       <c r="L13" t="n">
         <v>3.5279</v>
@@ -1468,19 +1468,19 @@
         <v>11.9117</v>
       </c>
       <c r="S13" t="n">
-        <v>-1.0936</v>
+        <v>-0.8184</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.3806999999999999</v>
+        <v>-0.1055</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.7126999999999999</v>
+        <v>-0.7129</v>
       </c>
       <c r="V13" t="n">
-        <v>1.2672</v>
+        <v>1.267199999999999</v>
       </c>
       <c r="W13" t="n">
-        <v>8.931299999999997</v>
+        <v>8.9313</v>
       </c>
       <c r="X13" t="n">
         <v>-7.6642</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>6.3597</v>
+        <v>5.1068</v>
       </c>
       <c r="E14" t="n">
-        <v>5.3789</v>
+        <v>4.2251</v>
       </c>
       <c r="F14" t="n">
-        <v>0.9808</v>
+        <v>0.8817</v>
       </c>
       <c r="G14" t="n">
         <v>3.0967</v>
@@ -1546,13 +1546,13 @@
         <v>2.0158</v>
       </c>
       <c r="S14" t="n">
-        <v>2.535</v>
+        <v>1.2821</v>
       </c>
       <c r="T14" t="n">
-        <v>1.9035</v>
+        <v>0.7496</v>
       </c>
       <c r="U14" t="n">
-        <v>0.6315</v>
+        <v>0.5324</v>
       </c>
       <c r="V14" t="n">
         <v>-1.2878</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>2.6125</v>
+        <v>3.0278</v>
       </c>
       <c r="E15" t="n">
-        <v>0.6401</v>
+        <v>0.8324</v>
       </c>
       <c r="F15" t="n">
-        <v>1.9725</v>
+        <v>2.1954</v>
       </c>
       <c r="G15" t="n">
         <v>0.0983</v>
@@ -1624,13 +1624,13 @@
         <v>2.0158</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.1455</v>
+        <v>0.2698</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.1847</v>
+        <v>0.0076</v>
       </c>
       <c r="U15" t="n">
-        <v>0.0393</v>
+        <v>0.2622</v>
       </c>
       <c r="V15" t="n">
         <v>0.6439</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>2.4919</v>
+        <v>2.7877</v>
       </c>
       <c r="E16" t="n">
-        <v>1.3171</v>
+        <v>1.5095</v>
       </c>
       <c r="F16" t="n">
-        <v>1.1748</v>
+        <v>1.2782</v>
       </c>
       <c r="G16" t="n">
         <v>2.9872</v>
@@ -1702,13 +1702,13 @@
         <v>2.0158</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.9509</v>
+        <v>-0.6552</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.7157</v>
+        <v>-0.5234</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.2352</v>
+        <v>-0.1318</v>
       </c>
       <c r="V16" t="n">
         <v>-0.6439</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.777</v>
+        <v>1.2957</v>
       </c>
       <c r="E17" t="n">
-        <v>-1.6842</v>
+        <v>-1.4919</v>
       </c>
       <c r="F17" t="n">
-        <v>2.4612</v>
+        <v>2.7876</v>
       </c>
       <c r="G17" t="n">
         <v>-0.7027</v>
@@ -1780,13 +1780,13 @@
         <v>2.1991</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.125</v>
+        <v>0.3937</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.0196</v>
+        <v>0.1727</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.1054</v>
+        <v>0.221</v>
       </c>
       <c r="V17" t="n">
         <v>0.3219</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>C. FAJARDO PANOS</t>
+          <t>J. JIMENEZ LORENTE</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,64 +1891,64 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.3115</v>
+        <v>-0.3305</v>
       </c>
       <c r="E19" t="n">
-        <v>0.7863</v>
+        <v>-0.7278</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.0978</v>
+        <v>0.3973</v>
       </c>
       <c r="G19" t="n">
-        <v>-1.4724</v>
+        <v>-0.008399999999999999</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.9052</v>
+        <v>0.5944</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.5672</v>
+        <v>-0.6028</v>
       </c>
       <c r="J19" t="n">
-        <v>0.1182</v>
+        <v>0.9962</v>
       </c>
       <c r="K19" t="n">
-        <v>0.1084</v>
+        <v>0.8296</v>
       </c>
       <c r="L19" t="n">
-        <v>0.0098</v>
+        <v>0.1667</v>
       </c>
       <c r="M19" t="n">
-        <v>-1.5907</v>
+        <v>-1.0047</v>
       </c>
       <c r="N19" t="n">
-        <v>-1.0136</v>
+        <v>-0.2351</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.5770999999999999</v>
+        <v>-0.7695</v>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>0.733</v>
       </c>
       <c r="Q19" t="n">
         <v>-0.9163</v>
       </c>
       <c r="R19" t="n">
-        <v>0.9163</v>
+        <v>1.6493</v>
       </c>
       <c r="S19" t="n">
-        <v>1.1609</v>
+        <v>-0.4216</v>
       </c>
       <c r="T19" t="n">
-        <v>1.2625</v>
+        <v>-0.4962</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.1015</v>
+        <v>0.0746</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>-0.6335</v>
       </c>
       <c r="W19" t="n">
-        <v>0.3219</v>
+        <v>-0.3115</v>
       </c>
       <c r="X19" t="n">
         <v>-0.3219</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>J. JIMENEZ LORENTE</t>
+          <t>H. RUEDA RIOS</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.7442</v>
+        <v>-0.7865</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.1124</v>
+        <v>-0.2764</v>
       </c>
       <c r="F20" t="n">
-        <v>0.3682</v>
+        <v>-0.5101</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.008399999999999999</v>
+        <v>-3.2806</v>
       </c>
       <c r="H20" t="n">
-        <v>0.5944</v>
+        <v>-1.0404</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.6028</v>
+        <v>-2.2403</v>
       </c>
       <c r="J20" t="n">
-        <v>0.9962</v>
+        <v>-1.609</v>
       </c>
       <c r="K20" t="n">
-        <v>0.8296</v>
+        <v>0.2785</v>
       </c>
       <c r="L20" t="n">
-        <v>0.1667</v>
+        <v>-1.8875</v>
       </c>
       <c r="M20" t="n">
-        <v>-1.0047</v>
+        <v>-1.6716</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.2351</v>
+        <v>-1.3189</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.7695</v>
+        <v>-0.3528</v>
       </c>
       <c r="P20" t="n">
-        <v>0.733</v>
+        <v>0.1833</v>
       </c>
       <c r="Q20" t="n">
-        <v>-0.9163</v>
+        <v>-1.8326</v>
       </c>
       <c r="R20" t="n">
-        <v>1.6493</v>
+        <v>2.0158</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.8353</v>
+        <v>0.4208</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.8808</v>
+        <v>0.3092</v>
       </c>
       <c r="U20" t="n">
-        <v>0.0455</v>
+        <v>0.1116</v>
       </c>
       <c r="V20" t="n">
-        <v>-0.6335</v>
+        <v>1.89</v>
       </c>
       <c r="W20" t="n">
-        <v>-0.3115</v>
+        <v>2.8559</v>
       </c>
       <c r="X20" t="n">
-        <v>-0.3219</v>
+        <v>-0.9658</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>H. RUEDA RIOS</t>
+          <t>C. FAJARDO PANOS</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.2585</v>
+        <v>-0.9555</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.0457</v>
+        <v>0.1133</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.2128</v>
+        <v>-1.0687</v>
       </c>
       <c r="G21" t="n">
-        <v>-3.2806</v>
+        <v>-1.4724</v>
       </c>
       <c r="H21" t="n">
-        <v>-1.0404</v>
+        <v>-0.9052</v>
       </c>
       <c r="I21" t="n">
-        <v>-2.2403</v>
+        <v>-0.5672</v>
       </c>
       <c r="J21" t="n">
-        <v>-1.609</v>
+        <v>0.1182</v>
       </c>
       <c r="K21" t="n">
-        <v>0.2785</v>
+        <v>0.1084</v>
       </c>
       <c r="L21" t="n">
-        <v>-1.8875</v>
+        <v>0.0098</v>
       </c>
       <c r="M21" t="n">
-        <v>-1.6716</v>
+        <v>-1.5907</v>
       </c>
       <c r="N21" t="n">
-        <v>-1.3189</v>
+        <v>-1.0136</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.3528</v>
+        <v>-0.5770999999999999</v>
       </c>
       <c r="P21" t="n">
-        <v>0.1833</v>
+        <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>-1.8326</v>
+        <v>-0.9163</v>
       </c>
       <c r="R21" t="n">
-        <v>2.0158</v>
+        <v>0.9163</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.0511</v>
+        <v>0.517</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.46</v>
+        <v>0.5894</v>
       </c>
       <c r="U21" t="n">
-        <v>0.4089</v>
+        <v>-0.07240000000000001</v>
       </c>
       <c r="V21" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="W21" t="n">
-        <v>2.8559</v>
+        <v>0.3219</v>
       </c>
       <c r="X21" t="n">
-        <v>-0.9658</v>
+        <v>-0.3219</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>G. CASASUS GOYENECHE</t>
+          <t>R. RAMOS SAN SEBASTIAN</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2125,73 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.3585</v>
+        <v>-1.5512</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.9539</v>
+        <v>-1.6682</v>
       </c>
       <c r="F22" t="n">
-        <v>0.5954</v>
+        <v>0.117</v>
       </c>
       <c r="G22" t="n">
-        <v>-2.0419</v>
+        <v>-2.3478</v>
       </c>
       <c r="H22" t="n">
-        <v>-1.5513</v>
+        <v>-0.7005</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.4905</v>
+        <v>-1.6473</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.9487</v>
+        <v>-1.7448</v>
       </c>
       <c r="K22" t="n">
-        <v>-1.0995</v>
+        <v>0.1268</v>
       </c>
       <c r="L22" t="n">
-        <v>0.1508</v>
+        <v>-1.8716</v>
       </c>
       <c r="M22" t="n">
-        <v>-1.0932</v>
+        <v>-0.603</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.4519</v>
+        <v>-0.8273</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.6413</v>
+        <v>0.2243</v>
       </c>
       <c r="P22" t="n">
-        <v>-0.9163</v>
+        <v>0.9163</v>
       </c>
       <c r="Q22" t="n">
-        <v>-3.6651</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>2.7489</v>
+        <v>0.9163</v>
       </c>
       <c r="S22" t="n">
-        <v>0.3327</v>
+        <v>-0.1197</v>
       </c>
       <c r="T22" t="n">
-        <v>0.126</v>
+        <v>0.0766</v>
       </c>
       <c r="U22" t="n">
-        <v>0.2068</v>
+        <v>-0.1963</v>
       </c>
       <c r="V22" t="n">
-        <v>1.267</v>
+        <v>0</v>
       </c>
       <c r="W22" t="n">
-        <v>2.5339</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>-1.267</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>R. RAMOS SAN SEBASTIAN</t>
+          <t>G. CASASUS GOYENECHE</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,67 +2203,67 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-1.6722</v>
+        <v>-1.6965</v>
       </c>
       <c r="E23" t="n">
-        <v>-1.7644</v>
+        <v>-2.2424</v>
       </c>
       <c r="F23" t="n">
-        <v>0.0922</v>
+        <v>0.5459000000000001</v>
       </c>
       <c r="G23" t="n">
-        <v>-2.3478</v>
+        <v>-2.0419</v>
       </c>
       <c r="H23" t="n">
-        <v>-0.7005</v>
+        <v>-1.5513</v>
       </c>
       <c r="I23" t="n">
-        <v>-1.6473</v>
+        <v>-0.4905</v>
       </c>
       <c r="J23" t="n">
-        <v>-1.7448</v>
+        <v>-0.9487</v>
       </c>
       <c r="K23" t="n">
-        <v>0.1268</v>
+        <v>-1.0995</v>
       </c>
       <c r="L23" t="n">
-        <v>-1.8716</v>
+        <v>0.1508</v>
       </c>
       <c r="M23" t="n">
-        <v>-0.603</v>
+        <v>-1.0932</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.8273</v>
+        <v>-0.4519</v>
       </c>
       <c r="O23" t="n">
-        <v>0.2243</v>
+        <v>-0.6413</v>
       </c>
       <c r="P23" t="n">
-        <v>0.9163</v>
+        <v>-0.9163</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>-3.6651</v>
       </c>
       <c r="R23" t="n">
-        <v>0.9163</v>
+        <v>2.7489</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.2406</v>
+        <v>-0.0053</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.0196</v>
+        <v>-0.1625</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.221</v>
+        <v>0.1572</v>
       </c>
       <c r="V23" t="n">
-        <v>0</v>
+        <v>1.267</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>2.5339</v>
       </c>
       <c r="X23" t="n">
-        <v>0</v>
+        <v>-1.267</v>
       </c>
     </row>
     <row r="24">
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-4.9888</v>
+        <v>-4.9291</v>
       </c>
       <c r="E24" t="n">
-        <v>-3.1567</v>
+        <v>-3.349</v>
       </c>
       <c r="F24" t="n">
-        <v>-1.8321</v>
+        <v>-1.58</v>
       </c>
       <c r="G24" t="n">
         <v>-4.5258</v>
@@ -2326,13 +2326,13 @@
         <v>2.5656</v>
       </c>
       <c r="S24" t="n">
-        <v>0.4295</v>
+        <v>0.4893</v>
       </c>
       <c r="T24" t="n">
-        <v>0.4917</v>
+        <v>0.2994</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.0622</v>
+        <v>0.1898</v>
       </c>
       <c r="V24" t="n">
         <v>-3.4581</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-6.8655</v>
+        <v>-6.2856</v>
       </c>
       <c r="E25" t="n">
-        <v>-5.7565</v>
+        <v>-5.2758</v>
       </c>
       <c r="F25" t="n">
-        <v>-1.1089</v>
+        <v>-1.0098</v>
       </c>
       <c r="G25" t="n">
         <v>-5.7498</v>
@@ -2404,13 +2404,13 @@
         <v>2.0158</v>
       </c>
       <c r="S25" t="n">
-        <v>-1.0161</v>
+        <v>-0.4363</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.7903</v>
+        <v>-0.3095</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.2258</v>
+        <v>-0.1267</v>
       </c>
       <c r="V25" t="n">
         <v>0.6335</v>
@@ -2437,13 +2437,13 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-4.632999999999999</v>
+        <v>-3.9918</v>
       </c>
       <c r="E26" t="n">
-        <v>-8.026299999999999</v>
+        <v>-8.0261</v>
       </c>
       <c r="F26" t="n">
-        <v>3.3935</v>
+        <v>4.0345</v>
       </c>
       <c r="G26" t="n">
         <v>-13.6221</v>
@@ -2482,13 +2482,13 @@
         <v>21.0745</v>
       </c>
       <c r="S26" t="n">
-        <v>1.0936</v>
+        <v>1.7346</v>
       </c>
       <c r="T26" t="n">
-        <v>0.7129999999999999</v>
+        <v>0.7129000000000002</v>
       </c>
       <c r="U26" t="n">
-        <v>0.3808999999999999</v>
+        <v>1.0216</v>
       </c>
       <c r="V26" t="n">
         <v>-1.267</v>
